--- a/reports/Debug-purgatory-20260104/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For Winter Ending (Prior Year)_Visits.xlsx
@@ -34,16 +34,16 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
     <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45601</v>
+        <v>45611</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45604</v>
+        <v>45612</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45605</v>
+        <v>45613</v>
       </c>
       <c r="C4" s="2">
-        <v>164</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45605</v>
+        <v>45614</v>
       </c>
       <c r="C5" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45612</v>
+        <v>45614</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C7" s="2">
-        <v>769</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -521,7 +521,7 @@
         <v>45615</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45618</v>
+        <v>45616</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C11" s="2">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -574,10 +574,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,10 +591,10 @@
         <v>45620</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45623</v>
+        <v>45621</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -633,10 +633,10 @@
         <v>45623</v>
       </c>
       <c r="C16" s="2">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C17" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45625</v>
+        <v>45624</v>
       </c>
       <c r="C18" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -700,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C21" s="2">
-        <v>297</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45626</v>
+        <v>45627</v>
       </c>
       <c r="C22" s="2">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45627</v>
+        <v>45630</v>
       </c>
       <c r="C23" s="2">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45629</v>
+        <v>45633</v>
       </c>
       <c r="C25" s="2">
-        <v>-3</v>
+        <v>295</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45629</v>
+        <v>45635</v>
       </c>
       <c r="C26" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45630</v>
+        <v>45636</v>
       </c>
       <c r="C27" s="2">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45631</v>
+        <v>45637</v>
       </c>
       <c r="C28" s="2">
-        <v>7</v>
+        <v>514</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45632</v>
+        <v>45638</v>
       </c>
       <c r="C29" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="C30" s="2">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45633</v>
+        <v>45639</v>
       </c>
       <c r="C31" s="2">
-        <v>1558</v>
+        <v>265</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45634</v>
+        <v>45640</v>
       </c>
       <c r="C32" s="2">
-        <v>160</v>
+        <v>1413</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45634</v>
+        <v>45642</v>
       </c>
       <c r="C33" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45636</v>
+        <v>45642</v>
       </c>
       <c r="C34" s="2">
-        <v>397</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45637</v>
+        <v>45642</v>
       </c>
       <c r="C35" s="2">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45637</v>
+        <v>45643</v>
       </c>
       <c r="C36" s="2">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45638</v>
+        <v>45643</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>468</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
       <c r="C38" s="2">
-        <v>573</v>
+        <v>94</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45640</v>
+        <v>45644</v>
       </c>
       <c r="C39" s="2">
-        <v>570</v>
+        <v>136</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45640</v>
+        <v>45645</v>
       </c>
       <c r="C40" s="2">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45641</v>
+        <v>45646</v>
       </c>
       <c r="C41" s="2">
+        <v>160</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45642</v>
+        <v>45646</v>
       </c>
       <c r="C42" s="2">
-        <v>479</v>
+        <v>838</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="C43" s="2">
-        <v>463</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45644</v>
+        <v>45646</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>45647</v>
       </c>
       <c r="C45" s="2">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="C46" s="2">
-        <v>14</v>
+        <v>363</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45648</v>
+        <v>45649</v>
       </c>
       <c r="C47" s="2">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45651</v>
+        <v>45650</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="C49" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="C50" s="2">
+        <v>324</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,10 +1123,10 @@
         <v>45652</v>
       </c>
       <c r="C51" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1137,10 +1137,10 @@
         <v>45652</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45653</v>
+        <v>45652</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45653</v>
+        <v>45655</v>
       </c>
       <c r="C54" s="2">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="C55" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45654</v>
+        <v>45656</v>
       </c>
       <c r="C56" s="2">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45655</v>
+        <v>45658</v>
       </c>
       <c r="C57" s="2">
-        <v>667</v>
+        <v>22</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45656</v>
+        <v>45658</v>
       </c>
       <c r="C58" s="2">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C60" s="2">
+        <v>311</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45657</v>
+        <v>45659</v>
       </c>
       <c r="C61" s="2">
-        <v>2</v>
+        <v>2084</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45658</v>
+        <v>45606</v>
       </c>
       <c r="C64" s="2">
-        <v>380</v>
+        <v>5</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45658</v>
+        <v>45610</v>
       </c>
       <c r="C65" s="2">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>8</v>
@@ -1330,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45658</v>
+        <v>45610</v>
       </c>
       <c r="C66" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45659</v>
+        <v>45612</v>
       </c>
       <c r="C67" s="2">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45660</v>
+        <v>45612</v>
       </c>
       <c r="C68" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45661</v>
+        <v>45613</v>
       </c>
       <c r="C69" s="2">
-        <v>487</v>
+        <v>44</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45604</v>
+        <v>45614</v>
       </c>
       <c r="C70" s="2">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,13 +1400,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45605</v>
+        <v>45616</v>
       </c>
       <c r="C71" s="2">
+        <v>15</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45606</v>
+        <v>45616</v>
       </c>
       <c r="C72" s="2">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,13 +1428,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45612</v>
+        <v>45617</v>
       </c>
       <c r="C73" s="2">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45613</v>
+        <v>45617</v>
       </c>
       <c r="C74" s="2">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45615</v>
+        <v>45618</v>
       </c>
       <c r="C75" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45615</v>
+        <v>45619</v>
       </c>
       <c r="C76" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45616</v>
+        <v>45620</v>
       </c>
       <c r="C77" s="2">
-        <v>181</v>
+        <v>541</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45619</v>
+        <v>45621</v>
       </c>
       <c r="C78" s="2">
-        <v>623</v>
+        <v>224</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45619</v>
+        <v>45621</v>
       </c>
       <c r="C79" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="C81" s="2">
-        <v>454</v>
+        <v>991</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C82" s="2">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45622</v>
+        <v>45624</v>
       </c>
       <c r="C83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1585,7 +1585,7 @@
         <v>45624</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1599,10 +1599,10 @@
         <v>45625</v>
       </c>
       <c r="C85" s="2">
-        <v>426</v>
+        <v>2</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>1024</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1624,13 +1624,13 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="C87" s="2">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1638,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45627</v>
+        <v>45634</v>
       </c>
       <c r="C88" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C89" s="2">
         <v>1</v>
@@ -1666,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45628</v>
+        <v>45636</v>
       </c>
       <c r="C90" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1680,10 +1680,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45628</v>
+        <v>45638</v>
       </c>
       <c r="C91" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1694,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>45631</v>
+        <v>45638</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>5</v>
@@ -1708,13 +1708,13 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>45631</v>
+        <v>45639</v>
       </c>
       <c r="C93" s="2">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>45634</v>
+        <v>45639</v>
       </c>
       <c r="C94" s="2">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1736,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>45634</v>
+        <v>45640</v>
       </c>
       <c r="C95" s="2">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>45635</v>
+        <v>45641</v>
       </c>
       <c r="C96" s="2">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>45636</v>
+        <v>45641</v>
       </c>
       <c r="C97" s="2">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C99" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,13 +1806,13 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>45638</v>
+        <v>45642</v>
       </c>
       <c r="C100" s="2">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1820,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>45638</v>
+        <v>45643</v>
       </c>
       <c r="C101" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,10 +1834,10 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
       <c r="C102" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>5</v>
@@ -1848,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>45640</v>
+        <v>45644</v>
       </c>
       <c r="C103" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>45641</v>
+        <v>45645</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -1876,13 +1876,13 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>45641</v>
+        <v>45645</v>
       </c>
       <c r="C105" s="2">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1890,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>45641</v>
+        <v>45645</v>
       </c>
       <c r="C106" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,13 +1904,13 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>45642</v>
+        <v>45645</v>
       </c>
       <c r="C107" s="2">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1918,10 +1918,10 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>45643</v>
+        <v>45646</v>
       </c>
       <c r="C108" s="2">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1932,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>45644</v>
+        <v>45647</v>
       </c>
       <c r="C109" s="2">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>5</v>
@@ -1946,13 +1946,13 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>45644</v>
+        <v>45648</v>
       </c>
       <c r="C110" s="2">
-        <v>41</v>
+        <v>273</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1960,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>45644</v>
+        <v>45649</v>
       </c>
       <c r="C111" s="2">
-        <v>3</v>
+        <v>969</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1974,13 +1974,13 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>45645</v>
+        <v>45650</v>
       </c>
       <c r="C112" s="2">
-        <v>550</v>
+        <v>1214</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1988,10 +1988,10 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -2002,13 +2002,13 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="C114" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>45648</v>
+        <v>45652</v>
       </c>
       <c r="C115" s="2">
-        <v>1184</v>
+        <v>1515</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2030,13 +2030,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="2">
-        <v>45650</v>
+        <v>45653</v>
       </c>
       <c r="C116" s="2">
-        <v>4</v>
+        <v>1862</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,10 +2044,10 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>45651</v>
+        <v>45653</v>
       </c>
       <c r="C117" s="2">
-        <v>1310</v>
+        <v>115</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>5</v>
@@ -2058,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>45651</v>
+        <v>45654</v>
       </c>
       <c r="C118" s="2">
-        <v>1274</v>
+        <v>5</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2072,10 +2072,10 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>45651</v>
+        <v>45655</v>
       </c>
       <c r="C119" s="2">
-        <v>63</v>
+        <v>1513</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2086,13 +2086,13 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="C120" s="2">
-        <v>6</v>
+        <v>2869</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2100,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>45654</v>
+        <v>45656</v>
       </c>
       <c r="C121" s="2">
-        <v>2065</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>5</v>
@@ -2114,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>45654</v>
+        <v>45656</v>
       </c>
       <c r="C122" s="2">
-        <v>2406</v>
+        <v>128</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2128,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>45654</v>
+        <v>45657</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>5</v>
@@ -2142,10 +2142,10 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>45654</v>
+        <v>45658</v>
       </c>
       <c r="C124" s="2">
-        <v>148</v>
+        <v>2027</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2156,13 +2156,13 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C125" s="2">
-        <v>2793</v>
+        <v>17</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2170,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C126" s="2">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>5</v>
@@ -2184,13 +2184,13 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>45657</v>
+        <v>45602</v>
       </c>
       <c r="C127" s="2">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2198,13 +2198,13 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>45658</v>
+        <v>45605</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2212,10 +2212,10 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>45659</v>
+        <v>45605</v>
       </c>
       <c r="C129" s="2">
-        <v>26</v>
+        <v>760</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>5</v>
@@ -2226,10 +2226,10 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>45660</v>
+        <v>45606</v>
       </c>
       <c r="C130" s="2">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>5</v>
@@ -2240,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>45660</v>
+        <v>45611</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2254,13 +2254,13 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>45660</v>
+        <v>45613</v>
       </c>
       <c r="C132" s="2">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2268,13 +2268,13 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>45660</v>
+        <v>45614</v>
       </c>
       <c r="C133" s="2">
-        <v>1871</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2282,10 +2282,10 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>45660</v>
+        <v>45614</v>
       </c>
       <c r="C134" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>5</v>
@@ -2296,13 +2296,13 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>45660</v>
+        <v>45616</v>
       </c>
       <c r="C135" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2310,10 +2310,10 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>45660</v>
+        <v>45617</v>
       </c>
       <c r="C136" s="2">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>5</v>
@@ -2324,13 +2324,13 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>45661</v>
+        <v>45619</v>
       </c>
       <c r="C137" s="2">
-        <v>6</v>
+        <v>224</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2338,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>45601</v>
+        <v>45620</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2352,10 +2352,10 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>45604</v>
+        <v>45621</v>
       </c>
       <c r="C139" s="2">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>8</v>
@@ -2366,10 +2366,10 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>45605</v>
+        <v>45623</v>
       </c>
       <c r="C140" s="2">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2380,13 +2380,13 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>45607</v>
+        <v>45623</v>
       </c>
       <c r="C141" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>45613</v>
+        <v>45625</v>
       </c>
       <c r="C142" s="2">
-        <v>2</v>
+        <v>707</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>5</v>
@@ -2408,10 +2408,10 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>45613</v>
+        <v>45626</v>
       </c>
       <c r="C143" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>5</v>
@@ -2422,13 +2422,13 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>45614</v>
+        <v>45626</v>
       </c>
       <c r="C144" s="2">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2436,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>45615</v>
+        <v>45626</v>
       </c>
       <c r="C145" s="2">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>5</v>
@@ -2450,13 +2450,13 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>45617</v>
+        <v>45627</v>
       </c>
       <c r="C146" s="2">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2464,10 +2464,10 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>45619</v>
+        <v>45627</v>
       </c>
       <c r="C147" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>5</v>
@@ -2478,13 +2478,13 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>45620</v>
+        <v>45628</v>
       </c>
       <c r="C148" s="2">
-        <v>245</v>
+        <v>337</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>45621</v>
+        <v>45629</v>
       </c>
       <c r="C149" s="2">
-        <v>412</v>
+        <v>5</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>5</v>
@@ -2506,10 +2506,10 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>45622</v>
+        <v>45630</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>5</v>
@@ -2520,10 +2520,10 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>45623</v>
+        <v>45631</v>
       </c>
       <c r="C151" s="2">
-        <v>349</v>
+        <v>16</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>6</v>
@@ -2534,10 +2534,10 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>45623</v>
+        <v>45631</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>5</v>
@@ -2548,10 +2548,10 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>45624</v>
+        <v>45632</v>
       </c>
       <c r="C153" s="2">
-        <v>957</v>
+        <v>114</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>5</v>
@@ -2562,10 +2562,10 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>45625</v>
+        <v>45632</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>5</v>
@@ -2576,10 +2576,10 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="C155" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>5</v>
@@ -2590,13 +2590,13 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>45627</v>
+        <v>45634</v>
       </c>
       <c r="C156" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2604,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>45627</v>
+        <v>45634</v>
       </c>
       <c r="C157" s="2">
-        <v>1018</v>
+        <v>1260</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2618,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>45627</v>
+        <v>45635</v>
       </c>
       <c r="C158" s="2">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>5</v>
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C159" s="2">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2646,10 +2646,10 @@
         <v>1</v>
       </c>
       <c r="B160" s="2">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="C160" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>5</v>
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B161" s="2">
-        <v>45630</v>
+        <v>45637</v>
       </c>
       <c r="C161" s="2">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2674,10 +2674,10 @@
         <v>1</v>
       </c>
       <c r="B162" s="2">
-        <v>45630</v>
+        <v>45638</v>
       </c>
       <c r="C162" s="2">
-        <v>392</v>
+        <v>102</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>5</v>
@@ -2688,10 +2688,10 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C163" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>5</v>
@@ -2702,13 +2702,13 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C164" s="2">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2716,10 +2716,10 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>45631</v>
+        <v>45641</v>
       </c>
       <c r="C165" s="2">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>5</v>
@@ -2730,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="B166" s="2">
-        <v>45632</v>
+        <v>45642</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2744,13 +2744,13 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>45633</v>
+        <v>45643</v>
       </c>
       <c r="C167" s="2">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2758,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>45633</v>
+        <v>45644</v>
       </c>
       <c r="C168" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2772,13 +2772,13 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>45634</v>
+        <v>45645</v>
       </c>
       <c r="C169" s="2">
-        <v>168</v>
+        <v>555</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2786,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>45636</v>
+        <v>45646</v>
       </c>
       <c r="C170" s="2">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2800,10 +2800,10 @@
         <v>1</v>
       </c>
       <c r="B171" s="2">
-        <v>45636</v>
+        <v>45647</v>
       </c>
       <c r="C171" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>5</v>
@@ -2814,13 +2814,13 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>45637</v>
+        <v>45647</v>
       </c>
       <c r="C172" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2828,10 +2828,10 @@
         <v>1</v>
       </c>
       <c r="B173" s="2">
-        <v>45639</v>
+        <v>45648</v>
       </c>
       <c r="C173" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>5</v>
@@ -2842,13 +2842,13 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>45640</v>
+        <v>45648</v>
       </c>
       <c r="C174" s="2">
-        <v>1</v>
+        <v>935</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2856,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>45640</v>
+        <v>45649</v>
       </c>
       <c r="C175" s="2">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2870,10 +2870,10 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>45642</v>
+        <v>45649</v>
       </c>
       <c r="C176" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>5</v>
@@ -2884,10 +2884,10 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>45645</v>
+        <v>45650</v>
       </c>
       <c r="C177" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>5</v>
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>45645</v>
+        <v>45650</v>
       </c>
       <c r="C178" s="2">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2912,10 +2912,10 @@
         <v>1</v>
       </c>
       <c r="B179" s="2">
-        <v>45645</v>
+        <v>45652</v>
       </c>
       <c r="C179" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>5</v>
@@ -2926,13 +2926,13 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>45646</v>
+        <v>45652</v>
       </c>
       <c r="C180" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2940,13 +2940,13 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>45646</v>
+        <v>45655</v>
       </c>
       <c r="C181" s="2">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2954,10 +2954,10 @@
         <v>1</v>
       </c>
       <c r="B182" s="2">
-        <v>45648</v>
+        <v>45655</v>
       </c>
       <c r="C182" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>5</v>
@@ -2968,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>45649</v>
+        <v>45655</v>
       </c>
       <c r="C183" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2982,13 +2982,13 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>45649</v>
+        <v>45655</v>
       </c>
       <c r="C184" s="2">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2996,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>45649</v>
+        <v>45656</v>
       </c>
       <c r="C185" s="2">
-        <v>1208</v>
+        <v>2</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3010,10 +3010,10 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>45651</v>
+        <v>45656</v>
       </c>
       <c r="C186" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>5</v>
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>45652</v>
+        <v>45657</v>
       </c>
       <c r="C187" s="2">
-        <v>6</v>
+        <v>1383</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>5</v>
@@ -3038,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>45652</v>
+        <v>45658</v>
       </c>
       <c r="C188" s="2">
-        <v>1348</v>
+        <v>4</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3052,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>45652</v>
+        <v>45658</v>
       </c>
       <c r="C189" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>5</v>
@@ -3066,10 +3066,10 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>45653</v>
+        <v>45658</v>
       </c>
       <c r="C190" s="2">
-        <v>1317</v>
+        <v>147</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>5</v>
@@ -3080,10 +3080,10 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>45654</v>
+        <v>45659</v>
       </c>
       <c r="C191" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3094,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>45655</v>
+        <v>45660</v>
       </c>
       <c r="C192" s="2">
-        <v>2</v>
+        <v>1733</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>5</v>
@@ -3108,10 +3108,10 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
       <c r="C193" s="2">
-        <v>1215</v>
+        <v>101</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>5</v>
@@ -3122,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>45657</v>
+        <v>45661</v>
       </c>
       <c r="C194" s="2">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>5</v>
@@ -3136,10 +3136,10 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C195" s="2">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3150,13 +3150,13 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>45659</v>
+        <v>45605</v>
       </c>
       <c r="C196" s="2">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3164,10 +3164,10 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>45659</v>
+        <v>45606</v>
       </c>
       <c r="C197" s="2">
-        <v>1567</v>
+        <v>499</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>5</v>
@@ -3178,13 +3178,13 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>45659</v>
+        <v>45606</v>
       </c>
       <c r="C198" s="2">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3192,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>45659</v>
+        <v>45606</v>
       </c>
       <c r="C199" s="2">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3206,13 +3206,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>45660</v>
+        <v>45612</v>
       </c>
       <c r="C200" s="2">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3220,10 +3220,10 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>45661</v>
+        <v>45612</v>
       </c>
       <c r="C201" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>5</v>
@@ -3234,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>45661</v>
+        <v>45614</v>
       </c>
       <c r="C202" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>5</v>
@@ -3248,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>45612</v>
+        <v>45615</v>
       </c>
       <c r="C203" s="2">
-        <v>987</v>
+        <v>2</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>5</v>
@@ -3262,13 +3262,13 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>45613</v>
+        <v>45615</v>
       </c>
       <c r="C204" s="2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3276,10 +3276,10 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C205" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>5</v>
@@ -3290,10 +3290,10 @@
         <v>1</v>
       </c>
       <c r="B206" s="2">
-        <v>45615</v>
+        <v>45618</v>
       </c>
       <c r="C206" s="2">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>5</v>
@@ -3304,13 +3304,13 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>45616</v>
+        <v>45619</v>
       </c>
       <c r="C207" s="2">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3318,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>45616</v>
+        <v>45620</v>
       </c>
       <c r="C208" s="2">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>5</v>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="B209" s="2">
-        <v>45617</v>
+        <v>45621</v>
       </c>
       <c r="C209" s="2">
         <v>1</v>
@@ -3346,13 +3346,13 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="C210" s="2">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3360,10 +3360,10 @@
         <v>1</v>
       </c>
       <c r="B211" s="2">
-        <v>45618</v>
+        <v>45622</v>
       </c>
       <c r="C211" s="2">
-        <v>343</v>
+        <v>1</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>5</v>
@@ -3374,13 +3374,13 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>45619</v>
+        <v>45622</v>
       </c>
       <c r="C212" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>45620</v>
+        <v>45623</v>
       </c>
       <c r="C213" s="2">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>5</v>
@@ -3402,10 +3402,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>45620</v>
+        <v>45624</v>
       </c>
       <c r="C214" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>5</v>
@@ -3416,13 +3416,13 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>45621</v>
+        <v>45624</v>
       </c>
       <c r="C215" s="2">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3430,10 +3430,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
       <c r="C216" s="2">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>5</v>
@@ -3444,13 +3444,13 @@
         <v>1</v>
       </c>
       <c r="B217" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C217" s="2">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3458,13 +3458,13 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C218" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3472,13 +3472,13 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C219" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3486,10 +3486,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="C220" s="2">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3500,10 +3500,10 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C221" s="2">
-        <v>410</v>
+        <v>15</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>6</v>
@@ -3514,10 +3514,10 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C222" s="2">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>5</v>
@@ -3531,10 +3531,10 @@
         <v>45629</v>
       </c>
       <c r="C223" s="2">
-        <v>85</v>
+        <v>368</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3542,13 +3542,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C224" s="2">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3556,10 +3556,10 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C225" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3570,10 +3570,10 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C226" s="2">
-        <v>2</v>
+        <v>580</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3584,10 +3584,10 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C227" s="2">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>5</v>
@@ -3598,10 +3598,10 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C228" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3612,13 +3612,13 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C229" s="2">
-        <v>160</v>
+        <v>457</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3626,13 +3626,13 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C230" s="2">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3640,10 +3640,10 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>5</v>
@@ -3654,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C232" s="2">
         <v>1</v>
@@ -3668,10 +3668,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C233" s="2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3682,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
@@ -3699,10 +3699,10 @@
         <v>45641</v>
       </c>
       <c r="C235" s="2">
-        <v>1125</v>
+        <v>403</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
@@ -3724,10 +3724,10 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C237" s="2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>5</v>
@@ -3738,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C238" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>5</v>
@@ -3752,10 +3752,10 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>45642</v>
+        <v>45644</v>
       </c>
       <c r="C239" s="2">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>5</v>
@@ -3766,10 +3766,10 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="C240" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>5</v>
@@ -3783,10 +3783,10 @@
         <v>45644</v>
       </c>
       <c r="C241" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3794,10 +3794,10 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="C242" s="2">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>5</v>
@@ -3808,10 +3808,10 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="C243" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>5</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="B244" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C244" s="2">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3836,13 +3836,13 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="C245" s="2">
-        <v>219</v>
+        <v>8</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>45647</v>
       </c>
       <c r="C246" s="2">
-        <v>1269</v>
+        <v>22</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>5</v>
@@ -3864,13 +3864,13 @@
         <v>1</v>
       </c>
       <c r="B247" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C247" s="2">
-        <v>139</v>
+        <v>819</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3878,10 +3878,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C248" s="2">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>5</v>
@@ -3892,10 +3892,10 @@
         <v>1</v>
       </c>
       <c r="B249" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C249" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>5</v>
@@ -3906,13 +3906,13 @@
         <v>1</v>
       </c>
       <c r="B250" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C250" s="2">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3920,13 +3920,13 @@
         <v>1</v>
       </c>
       <c r="B251" s="2">
-        <v>45650</v>
+        <v>45649</v>
       </c>
       <c r="C251" s="2">
-        <v>316</v>
+        <v>94</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>45650</v>
       </c>
       <c r="C252" s="2">
-        <v>963</v>
+        <v>9</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>5</v>
@@ -3951,10 +3951,10 @@
         <v>45650</v>
       </c>
       <c r="C253" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>45651</v>
       </c>
       <c r="C254" s="2">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>5</v>
@@ -3976,10 +3976,10 @@
         <v>1</v>
       </c>
       <c r="B255" s="2">
-        <v>45653</v>
+        <v>45651</v>
       </c>
       <c r="C255" s="2">
-        <v>495</v>
+        <v>-7</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>8</v>
@@ -3990,13 +3990,13 @@
         <v>1</v>
       </c>
       <c r="B256" s="2">
-        <v>45653</v>
+        <v>45651</v>
       </c>
       <c r="C256" s="2">
-        <v>29</v>
+        <v>327</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4004,10 +4004,10 @@
         <v>1</v>
       </c>
       <c r="B257" s="2">
-        <v>45654</v>
+        <v>45652</v>
       </c>
       <c r="C257" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>5</v>
@@ -4018,13 +4018,13 @@
         <v>1</v>
       </c>
       <c r="B258" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C258" s="2">
-        <v>2640</v>
+        <v>4</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4032,10 +4032,10 @@
         <v>1</v>
       </c>
       <c r="B259" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C259" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>5</v>
@@ -4046,13 +4046,13 @@
         <v>1</v>
       </c>
       <c r="B260" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C260" s="2">
-        <v>808</v>
+        <v>6</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4060,13 +4060,13 @@
         <v>1</v>
       </c>
       <c r="B261" s="2">
-        <v>45657</v>
+        <v>45653</v>
       </c>
       <c r="C261" s="2">
-        <v>313</v>
+        <v>2</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4074,13 +4074,13 @@
         <v>1</v>
       </c>
       <c r="B262" s="2">
-        <v>45658</v>
+        <v>45654</v>
       </c>
       <c r="C262" s="2">
-        <v>2335</v>
+        <v>2</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4088,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="B263" s="2">
-        <v>45659</v>
+        <v>45654</v>
       </c>
       <c r="C263" s="2">
-        <v>38</v>
+        <v>592</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4102,13 +4102,13 @@
         <v>1</v>
       </c>
       <c r="B264" s="2">
-        <v>45659</v>
+        <v>45655</v>
       </c>
       <c r="C264" s="2">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4116,10 +4116,10 @@
         <v>1</v>
       </c>
       <c r="B265" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C265" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>5</v>
@@ -4130,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="B266" s="2">
-        <v>45660</v>
+        <v>45657</v>
       </c>
       <c r="C266" s="2">
-        <v>303</v>
+        <v>851</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4144,13 +4144,13 @@
         <v>1</v>
       </c>
       <c r="B267" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C267" s="2">
-        <v>1656</v>
+        <v>20</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4158,10 +4158,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="2">
-        <v>45606</v>
+        <v>45658</v>
       </c>
       <c r="C268" s="2">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>5</v>
@@ -4172,13 +4172,13 @@
         <v>1</v>
       </c>
       <c r="B269" s="2">
-        <v>45610</v>
+        <v>45659</v>
       </c>
       <c r="C269" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4186,13 +4186,13 @@
         <v>1</v>
       </c>
       <c r="B270" s="2">
-        <v>45610</v>
+        <v>45660</v>
       </c>
       <c r="C270" s="2">
+        <v>672</v>
+      </c>
+      <c r="D270" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4200,13 +4200,13 @@
         <v>1</v>
       </c>
       <c r="B271" s="2">
-        <v>45612</v>
+        <v>45660</v>
       </c>
       <c r="C271" s="2">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4214,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="B272" s="2">
-        <v>45612</v>
+        <v>45661</v>
       </c>
       <c r="C272" s="2">
-        <v>12</v>
+        <v>1965</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>5</v>
@@ -4228,13 +4228,13 @@
         <v>1</v>
       </c>
       <c r="B273" s="2">
-        <v>45613</v>
+        <v>45601</v>
       </c>
       <c r="C273" s="2">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4242,10 +4242,10 @@
         <v>1</v>
       </c>
       <c r="B274" s="2">
-        <v>45614</v>
+        <v>45604</v>
       </c>
       <c r="C274" s="2">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>5</v>
@@ -4256,13 +4256,13 @@
         <v>1</v>
       </c>
       <c r="B275" s="2">
-        <v>45616</v>
+        <v>45605</v>
       </c>
       <c r="C275" s="2">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4270,10 +4270,10 @@
         <v>1</v>
       </c>
       <c r="B276" s="2">
-        <v>45616</v>
+        <v>45605</v>
       </c>
       <c r="C276" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>5</v>
@@ -4284,10 +4284,10 @@
         <v>1</v>
       </c>
       <c r="B277" s="2">
-        <v>45617</v>
+        <v>45612</v>
       </c>
       <c r="C277" s="2">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>5</v>
@@ -4298,10 +4298,10 @@
         <v>1</v>
       </c>
       <c r="B278" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C278" s="2">
-        <v>234</v>
+        <v>769</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>5</v>
@@ -4312,13 +4312,13 @@
         <v>1</v>
       </c>
       <c r="B279" s="2">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="C279" s="2">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4326,13 +4326,13 @@
         <v>1</v>
       </c>
       <c r="B280" s="2">
-        <v>45619</v>
+        <v>45618</v>
       </c>
       <c r="C280" s="2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4340,10 +4340,10 @@
         <v>1</v>
       </c>
       <c r="B281" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C281" s="2">
-        <v>541</v>
+        <v>2</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>5</v>
@@ -4354,13 +4354,13 @@
         <v>1</v>
       </c>
       <c r="B282" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C282" s="2">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4368,10 +4368,10 @@
         <v>1</v>
       </c>
       <c r="B283" s="2">
-        <v>45621</v>
+        <v>45619</v>
       </c>
       <c r="C283" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>5</v>
@@ -4382,13 +4382,13 @@
         <v>1</v>
       </c>
       <c r="B284" s="2">
-        <v>45622</v>
+        <v>45620</v>
       </c>
       <c r="C284" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4396,10 +4396,10 @@
         <v>1</v>
       </c>
       <c r="B285" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C285" s="2">
-        <v>991</v>
+        <v>1</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>5</v>
@@ -4410,13 +4410,13 @@
         <v>1</v>
       </c>
       <c r="B286" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C286" s="2">
-        <v>340</v>
+        <v>1</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4424,13 +4424,13 @@
         <v>1</v>
       </c>
       <c r="B287" s="2">
-        <v>45624</v>
+        <v>45623</v>
       </c>
       <c r="C287" s="2">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>45624</v>
       </c>
       <c r="C288" s="2">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>5</v>
@@ -4455,7 +4455,7 @@
         <v>45625</v>
       </c>
       <c r="C289" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>5</v>
@@ -4466,10 +4466,10 @@
         <v>1</v>
       </c>
       <c r="B290" s="2">
-        <v>45626</v>
+        <v>45625</v>
       </c>
       <c r="C290" s="2">
-        <v>1024</v>
+        <v>4</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>5</v>
@@ -4480,13 +4480,13 @@
         <v>1</v>
       </c>
       <c r="B291" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C291" s="2">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4494,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="B292" s="2">
-        <v>45634</v>
+        <v>45626</v>
       </c>
       <c r="C292" s="2">
-        <v>5</v>
+        <v>297</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4508,13 +4508,13 @@
         <v>1</v>
       </c>
       <c r="B293" s="2">
-        <v>45635</v>
+        <v>45626</v>
       </c>
       <c r="C293" s="2">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4522,10 +4522,10 @@
         <v>1</v>
       </c>
       <c r="B294" s="2">
-        <v>45636</v>
+        <v>45627</v>
       </c>
       <c r="C294" s="2">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>5</v>
@@ -4536,7 +4536,7 @@
         <v>1</v>
       </c>
       <c r="B295" s="2">
-        <v>45638</v>
+        <v>45628</v>
       </c>
       <c r="C295" s="2">
         <v>1</v>
@@ -4550,13 +4550,13 @@
         <v>1</v>
       </c>
       <c r="B296" s="2">
-        <v>45638</v>
+        <v>45629</v>
       </c>
       <c r="C296" s="2">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4564,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="B297" s="2">
-        <v>45639</v>
+        <v>45629</v>
       </c>
       <c r="C297" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4578,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="B298" s="2">
-        <v>45639</v>
+        <v>45630</v>
       </c>
       <c r="C298" s="2">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4592,10 +4592,10 @@
         <v>1</v>
       </c>
       <c r="B299" s="2">
-        <v>45640</v>
+        <v>45631</v>
       </c>
       <c r="C299" s="2">
-        <v>145</v>
+        <v>7</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>5</v>
@@ -4606,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="B300" s="2">
-        <v>45641</v>
+        <v>45632</v>
       </c>
       <c r="C300" s="2">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4620,10 +4620,10 @@
         <v>1</v>
       </c>
       <c r="B301" s="2">
-        <v>45641</v>
+        <v>45633</v>
       </c>
       <c r="C301" s="2">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>5</v>
@@ -4634,10 +4634,10 @@
         <v>1</v>
       </c>
       <c r="B302" s="2">
-        <v>45641</v>
+        <v>45633</v>
       </c>
       <c r="C302" s="2">
-        <v>6</v>
+        <v>1558</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>5</v>
@@ -4648,13 +4648,13 @@
         <v>1</v>
       </c>
       <c r="B303" s="2">
-        <v>45641</v>
+        <v>45634</v>
       </c>
       <c r="C303" s="2">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4662,13 +4662,13 @@
         <v>1</v>
       </c>
       <c r="B304" s="2">
-        <v>45642</v>
+        <v>45634</v>
       </c>
       <c r="C304" s="2">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4676,10 +4676,10 @@
         <v>1</v>
       </c>
       <c r="B305" s="2">
-        <v>45643</v>
+        <v>45636</v>
       </c>
       <c r="C305" s="2">
-        <v>4</v>
+        <v>397</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>5</v>
@@ -4690,13 +4690,13 @@
         <v>1</v>
       </c>
       <c r="B306" s="2">
-        <v>45643</v>
+        <v>45637</v>
       </c>
       <c r="C306" s="2">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4704,10 +4704,10 @@
         <v>1</v>
       </c>
       <c r="B307" s="2">
-        <v>45644</v>
+        <v>45637</v>
       </c>
       <c r="C307" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>5</v>
@@ -4718,13 +4718,13 @@
         <v>1</v>
       </c>
       <c r="B308" s="2">
-        <v>45645</v>
+        <v>45638</v>
       </c>
       <c r="C308" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4732,13 +4732,13 @@
         <v>1</v>
       </c>
       <c r="B309" s="2">
-        <v>45645</v>
+        <v>45639</v>
       </c>
       <c r="C309" s="2">
-        <v>4</v>
+        <v>573</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4746,13 +4746,13 @@
         <v>1</v>
       </c>
       <c r="B310" s="2">
-        <v>45645</v>
+        <v>45640</v>
       </c>
       <c r="C310" s="2">
-        <v>79</v>
+        <v>570</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4760,13 +4760,13 @@
         <v>1</v>
       </c>
       <c r="B311" s="2">
-        <v>45645</v>
+        <v>45640</v>
       </c>
       <c r="C311" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4774,10 +4774,10 @@
         <v>1</v>
       </c>
       <c r="B312" s="2">
-        <v>45646</v>
+        <v>45641</v>
       </c>
       <c r="C312" s="2">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>5</v>
@@ -4788,10 +4788,10 @@
         <v>1</v>
       </c>
       <c r="B313" s="2">
-        <v>45647</v>
+        <v>45642</v>
       </c>
       <c r="C313" s="2">
-        <v>69</v>
+        <v>479</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>5</v>
@@ -4802,13 +4802,13 @@
         <v>1</v>
       </c>
       <c r="B314" s="2">
-        <v>45648</v>
+        <v>45643</v>
       </c>
       <c r="C314" s="2">
-        <v>273</v>
+        <v>463</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4816,10 +4816,10 @@
         <v>1</v>
       </c>
       <c r="B315" s="2">
-        <v>45649</v>
+        <v>45644</v>
       </c>
       <c r="C315" s="2">
-        <v>969</v>
+        <v>1</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>5</v>
@@ -4830,13 +4830,13 @@
         <v>1</v>
       </c>
       <c r="B316" s="2">
-        <v>45650</v>
+        <v>45647</v>
       </c>
       <c r="C316" s="2">
-        <v>1214</v>
+        <v>10</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4844,10 +4844,10 @@
         <v>1</v>
       </c>
       <c r="B317" s="2">
-        <v>45650</v>
+        <v>45648</v>
       </c>
       <c r="C317" s="2">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>5</v>
@@ -4858,13 +4858,13 @@
         <v>1</v>
       </c>
       <c r="B318" s="2">
-        <v>45651</v>
+        <v>45648</v>
       </c>
       <c r="C318" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4872,10 +4872,10 @@
         <v>1</v>
       </c>
       <c r="B319" s="2">
-        <v>45652</v>
+        <v>45651</v>
       </c>
       <c r="C319" s="2">
-        <v>1515</v>
+        <v>4</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>5</v>
@@ -4886,13 +4886,13 @@
         <v>1</v>
       </c>
       <c r="B320" s="2">
-        <v>45653</v>
+        <v>45651</v>
       </c>
       <c r="C320" s="2">
-        <v>1862</v>
+        <v>15</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4900,10 +4900,10 @@
         <v>1</v>
       </c>
       <c r="B321" s="2">
-        <v>45653</v>
+        <v>45651</v>
       </c>
       <c r="C321" s="2">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>5</v>
@@ -4914,10 +4914,10 @@
         <v>1</v>
       </c>
       <c r="B322" s="2">
-        <v>45654</v>
+        <v>45652</v>
       </c>
       <c r="C322" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>5</v>
@@ -4928,13 +4928,13 @@
         <v>1</v>
       </c>
       <c r="B323" s="2">
-        <v>45655</v>
+        <v>45652</v>
       </c>
       <c r="C323" s="2">
-        <v>1513</v>
+        <v>3</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4942,13 +4942,13 @@
         <v>1</v>
       </c>
       <c r="B324" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C324" s="2">
-        <v>2869</v>
+        <v>1</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="B325" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C325" s="2">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>5</v>
@@ -4970,10 +4970,10 @@
         <v>1</v>
       </c>
       <c r="B326" s="2">
-        <v>45656</v>
+        <v>45654</v>
       </c>
       <c r="C326" s="2">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>5</v>
@@ -4984,10 +4984,10 @@
         <v>1</v>
       </c>
       <c r="B327" s="2">
-        <v>45657</v>
+        <v>45654</v>
       </c>
       <c r="C327" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>5</v>
@@ -4998,13 +4998,13 @@
         <v>1</v>
       </c>
       <c r="B328" s="2">
-        <v>45658</v>
+        <v>45655</v>
       </c>
       <c r="C328" s="2">
-        <v>2027</v>
+        <v>667</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5012,10 +5012,10 @@
         <v>1</v>
       </c>
       <c r="B329" s="2">
-        <v>45660</v>
+        <v>45656</v>
       </c>
       <c r="C329" s="2">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>5</v>
@@ -5026,10 +5026,10 @@
         <v>1</v>
       </c>
       <c r="B330" s="2">
-        <v>45661</v>
+        <v>45657</v>
       </c>
       <c r="C330" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>5</v>
@@ -5040,10 +5040,10 @@
         <v>1</v>
       </c>
       <c r="B331" s="2">
-        <v>45605</v>
+        <v>45657</v>
       </c>
       <c r="C331" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>5</v>
@@ -5054,10 +5054,10 @@
         <v>1</v>
       </c>
       <c r="B332" s="2">
-        <v>45606</v>
+        <v>45657</v>
       </c>
       <c r="C332" s="2">
-        <v>499</v>
+        <v>2</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>5</v>
@@ -5068,13 +5068,13 @@
         <v>1</v>
       </c>
       <c r="B333" s="2">
-        <v>45606</v>
+        <v>45657</v>
       </c>
       <c r="C333" s="2">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5082,10 +5082,10 @@
         <v>1</v>
       </c>
       <c r="B334" s="2">
-        <v>45606</v>
+        <v>45658</v>
       </c>
       <c r="C334" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>5</v>
@@ -5096,13 +5096,13 @@
         <v>1</v>
       </c>
       <c r="B335" s="2">
-        <v>45612</v>
+        <v>45658</v>
       </c>
       <c r="C335" s="2">
-        <v>222</v>
+        <v>380</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5110,13 +5110,13 @@
         <v>1</v>
       </c>
       <c r="B336" s="2">
-        <v>45612</v>
+        <v>45658</v>
       </c>
       <c r="C336" s="2">
-        <v>14</v>
+        <v>684</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5124,13 +5124,13 @@
         <v>1</v>
       </c>
       <c r="B337" s="2">
-        <v>45614</v>
+        <v>45658</v>
       </c>
       <c r="C337" s="2">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5138,10 +5138,10 @@
         <v>1</v>
       </c>
       <c r="B338" s="2">
-        <v>45615</v>
+        <v>45659</v>
       </c>
       <c r="C338" s="2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>5</v>
@@ -5152,13 +5152,13 @@
         <v>1</v>
       </c>
       <c r="B339" s="2">
-        <v>45615</v>
+        <v>45660</v>
       </c>
       <c r="C339" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5166,13 +5166,13 @@
         <v>1</v>
       </c>
       <c r="B340" s="2">
-        <v>45615</v>
+        <v>45661</v>
       </c>
       <c r="C340" s="2">
-        <v>2</v>
+        <v>487</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5180,10 +5180,10 @@
         <v>1</v>
       </c>
       <c r="B341" s="2">
-        <v>45618</v>
+        <v>45604</v>
       </c>
       <c r="C341" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>5</v>
@@ -5194,13 +5194,13 @@
         <v>1</v>
       </c>
       <c r="B342" s="2">
-        <v>45619</v>
+        <v>45605</v>
       </c>
       <c r="C342" s="2">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5208,13 +5208,13 @@
         <v>1</v>
       </c>
       <c r="B343" s="2">
-        <v>45620</v>
+        <v>45606</v>
       </c>
       <c r="C343" s="2">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5222,13 +5222,13 @@
         <v>1</v>
       </c>
       <c r="B344" s="2">
-        <v>45621</v>
+        <v>45612</v>
       </c>
       <c r="C344" s="2">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5236,10 +5236,10 @@
         <v>1</v>
       </c>
       <c r="B345" s="2">
-        <v>45621</v>
+        <v>45613</v>
       </c>
       <c r="C345" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>5</v>
@@ -5250,13 +5250,13 @@
         <v>1</v>
       </c>
       <c r="B346" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C346" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5264,13 +5264,13 @@
         <v>1</v>
       </c>
       <c r="B347" s="2">
-        <v>45622</v>
+        <v>45615</v>
       </c>
       <c r="C347" s="2">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5278,10 +5278,10 @@
         <v>1</v>
       </c>
       <c r="B348" s="2">
-        <v>45623</v>
+        <v>45616</v>
       </c>
       <c r="C348" s="2">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>5</v>
@@ -5292,10 +5292,10 @@
         <v>1</v>
       </c>
       <c r="B349" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C349" s="2">
-        <v>3</v>
+        <v>623</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>5</v>
@@ -5306,10 +5306,10 @@
         <v>1</v>
       </c>
       <c r="B350" s="2">
-        <v>45624</v>
+        <v>45619</v>
       </c>
       <c r="C350" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>5</v>
@@ -5320,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="B351" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C351" s="2">
         <v>1</v>
@@ -5334,13 +5334,13 @@
         <v>1</v>
       </c>
       <c r="B352" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C352" s="2">
-        <v>159</v>
+        <v>454</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5348,13 +5348,13 @@
         <v>1</v>
       </c>
       <c r="B353" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C353" s="2">
-        <v>132</v>
+        <v>284</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5362,13 +5362,13 @@
         <v>1</v>
       </c>
       <c r="B354" s="2">
-        <v>45625</v>
+        <v>45622</v>
       </c>
       <c r="C354" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5376,10 +5376,10 @@
         <v>1</v>
       </c>
       <c r="B355" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C355" s="2">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>5</v>
@@ -5390,13 +5390,13 @@
         <v>1</v>
       </c>
       <c r="B356" s="2">
-        <v>45628</v>
+        <v>45625</v>
       </c>
       <c r="C356" s="2">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5404,10 +5404,10 @@
         <v>1</v>
       </c>
       <c r="B357" s="2">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="C357" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>5</v>
@@ -5418,10 +5418,10 @@
         <v>1</v>
       </c>
       <c r="B358" s="2">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="C358" s="2">
-        <v>368</v>
+        <v>28</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>5</v>
@@ -5432,13 +5432,13 @@
         <v>1</v>
       </c>
       <c r="B359" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C359" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5446,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="B360" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C360" s="2">
         <v>1</v>
@@ -5460,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="B361" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C361" s="2">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5474,10 +5474,10 @@
         <v>1</v>
       </c>
       <c r="B362" s="2">
-        <v>45635</v>
+        <v>45628</v>
       </c>
       <c r="C362" s="2">
-        <v>360</v>
+        <v>8</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>5</v>
@@ -5488,10 +5488,10 @@
         <v>1</v>
       </c>
       <c r="B363" s="2">
-        <v>45635</v>
+        <v>45631</v>
       </c>
       <c r="C363" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>5</v>
@@ -5502,13 +5502,13 @@
         <v>1</v>
       </c>
       <c r="B364" s="2">
-        <v>45638</v>
+        <v>45631</v>
       </c>
       <c r="C364" s="2">
-        <v>457</v>
+        <v>89</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5516,13 +5516,13 @@
         <v>1</v>
       </c>
       <c r="B365" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C365" s="2">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5530,10 +5530,10 @@
         <v>1</v>
       </c>
       <c r="B366" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C366" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>5</v>
@@ -5544,13 +5544,13 @@
         <v>1</v>
       </c>
       <c r="B367" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C367" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5558,10 +5558,10 @@
         <v>1</v>
       </c>
       <c r="B368" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C368" s="2">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>5</v>
@@ -5572,7 +5572,7 @@
         <v>1</v>
       </c>
       <c r="B369" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C369" s="2">
         <v>1</v>
@@ -5586,13 +5586,13 @@
         <v>1</v>
       </c>
       <c r="B370" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C370" s="2">
-        <v>403</v>
+        <v>2</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5600,10 +5600,10 @@
         <v>1</v>
       </c>
       <c r="B371" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C371" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>5</v>
@@ -5614,13 +5614,13 @@
         <v>1</v>
       </c>
       <c r="B372" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C372" s="2">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5628,10 +5628,10 @@
         <v>1</v>
       </c>
       <c r="B373" s="2">
-        <v>45643</v>
+        <v>45639</v>
       </c>
       <c r="C373" s="2">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>5</v>
@@ -5642,10 +5642,10 @@
         <v>1</v>
       </c>
       <c r="B374" s="2">
-        <v>45644</v>
+        <v>45640</v>
       </c>
       <c r="C374" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>5</v>
@@ -5656,10 +5656,10 @@
         <v>1</v>
       </c>
       <c r="B375" s="2">
-        <v>45644</v>
+        <v>45641</v>
       </c>
       <c r="C375" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>5</v>
@@ -5670,13 +5670,13 @@
         <v>1</v>
       </c>
       <c r="B376" s="2">
-        <v>45644</v>
+        <v>45641</v>
       </c>
       <c r="C376" s="2">
-        <v>482</v>
+        <v>99</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5684,13 +5684,13 @@
         <v>1</v>
       </c>
       <c r="B377" s="2">
-        <v>45644</v>
+        <v>45641</v>
       </c>
       <c r="C377" s="2">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5698,10 +5698,10 @@
         <v>1</v>
       </c>
       <c r="B378" s="2">
-        <v>45644</v>
+        <v>45642</v>
       </c>
       <c r="C378" s="2">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>5</v>
@@ -5712,10 +5712,10 @@
         <v>1</v>
       </c>
       <c r="B379" s="2">
-        <v>45644</v>
+        <v>45643</v>
       </c>
       <c r="C379" s="2">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D379" s="2" t="s">
         <v>5</v>
@@ -5726,10 +5726,10 @@
         <v>1</v>
       </c>
       <c r="B380" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C380" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>5</v>
@@ -5740,13 +5740,13 @@
         <v>1</v>
       </c>
       <c r="B381" s="2">
-        <v>45647</v>
+        <v>45644</v>
       </c>
       <c r="C381" s="2">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5754,13 +5754,13 @@
         <v>1</v>
       </c>
       <c r="B382" s="2">
-        <v>45647</v>
+        <v>45644</v>
       </c>
       <c r="C382" s="2">
-        <v>819</v>
+        <v>3</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5768,10 +5768,10 @@
         <v>1</v>
       </c>
       <c r="B383" s="2">
-        <v>45647</v>
+        <v>45645</v>
       </c>
       <c r="C383" s="2">
-        <v>13</v>
+        <v>550</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>5</v>
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="B384" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C384" s="2">
         <v>1</v>
@@ -5796,13 +5796,13 @@
         <v>1</v>
       </c>
       <c r="B385" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C385" s="2">
-        <v>244</v>
+        <v>4</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5810,10 +5810,10 @@
         <v>1</v>
       </c>
       <c r="B386" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C386" s="2">
-        <v>94</v>
+        <v>1184</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>5</v>
@@ -5827,7 +5827,7 @@
         <v>45650</v>
       </c>
       <c r="C387" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>5</v>
@@ -5838,10 +5838,10 @@
         <v>1</v>
       </c>
       <c r="B388" s="2">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="C388" s="2">
-        <v>12</v>
+        <v>1310</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>5</v>
@@ -5855,10 +5855,10 @@
         <v>45651</v>
       </c>
       <c r="C389" s="2">
-        <v>1</v>
+        <v>1274</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5869,10 +5869,10 @@
         <v>45651</v>
       </c>
       <c r="C390" s="2">
-        <v>-7</v>
+        <v>63</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5880,13 +5880,13 @@
         <v>1</v>
       </c>
       <c r="B391" s="2">
-        <v>45651</v>
+        <v>45653</v>
       </c>
       <c r="C391" s="2">
-        <v>327</v>
+        <v>6</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5894,10 +5894,10 @@
         <v>1</v>
       </c>
       <c r="B392" s="2">
-        <v>45652</v>
+        <v>45654</v>
       </c>
       <c r="C392" s="2">
-        <v>120</v>
+        <v>2065</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>5</v>
@@ -5908,13 +5908,13 @@
         <v>1</v>
       </c>
       <c r="B393" s="2">
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="C393" s="2">
-        <v>4</v>
+        <v>2406</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5922,10 +5922,10 @@
         <v>1</v>
       </c>
       <c r="B394" s="2">
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="C394" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>5</v>
@@ -5936,10 +5936,10 @@
         <v>1</v>
       </c>
       <c r="B395" s="2">
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="C395" s="2">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>5</v>
@@ -5950,13 +5950,13 @@
         <v>1</v>
       </c>
       <c r="B396" s="2">
-        <v>45653</v>
+        <v>45657</v>
       </c>
       <c r="C396" s="2">
-        <v>2</v>
+        <v>2793</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5964,10 +5964,10 @@
         <v>1</v>
       </c>
       <c r="B397" s="2">
-        <v>45654</v>
+        <v>45657</v>
       </c>
       <c r="C397" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D397" s="2" t="s">
         <v>5</v>
@@ -5978,13 +5978,13 @@
         <v>1</v>
       </c>
       <c r="B398" s="2">
-        <v>45654</v>
+        <v>45657</v>
       </c>
       <c r="C398" s="2">
-        <v>592</v>
+        <v>122</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5992,10 +5992,10 @@
         <v>1</v>
       </c>
       <c r="B399" s="2">
-        <v>45655</v>
+        <v>45658</v>
       </c>
       <c r="C399" s="2">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>5</v>
@@ -6006,10 +6006,10 @@
         <v>1</v>
       </c>
       <c r="B400" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
       <c r="C400" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>5</v>
@@ -6020,13 +6020,13 @@
         <v>1</v>
       </c>
       <c r="B401" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C401" s="2">
-        <v>851</v>
+        <v>1</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6034,13 +6034,13 @@
         <v>1</v>
       </c>
       <c r="B402" s="2">
-        <v>45657</v>
+        <v>45660</v>
       </c>
       <c r="C402" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6048,10 +6048,10 @@
         <v>1</v>
       </c>
       <c r="B403" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C403" s="2">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D403" s="2" t="s">
         <v>5</v>
@@ -6062,13 +6062,13 @@
         <v>1</v>
       </c>
       <c r="B404" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C404" s="2">
-        <v>2</v>
+        <v>1871</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6079,10 +6079,10 @@
         <v>45660</v>
       </c>
       <c r="C405" s="2">
-        <v>672</v>
+        <v>2</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6096,7 +6096,7 @@
         <v>26</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6104,10 +6104,10 @@
         <v>1</v>
       </c>
       <c r="B407" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C407" s="2">
-        <v>1965</v>
+        <v>179</v>
       </c>
       <c r="D407" s="2" t="s">
         <v>5</v>
@@ -6118,13 +6118,13 @@
         <v>1</v>
       </c>
       <c r="B408" s="2">
-        <v>45611</v>
+        <v>45661</v>
       </c>
       <c r="C408" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6135,7 +6135,7 @@
         <v>45612</v>
       </c>
       <c r="C409" s="2">
-        <v>129</v>
+        <v>987</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>5</v>
@@ -6163,10 +6163,10 @@
         <v>45614</v>
       </c>
       <c r="C411" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6174,10 +6174,10 @@
         <v>1</v>
       </c>
       <c r="B412" s="2">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="C412" s="2">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D412" s="2" t="s">
         <v>5</v>
@@ -6188,10 +6188,10 @@
         <v>1</v>
       </c>
       <c r="B413" s="2">
-        <v>45614</v>
+        <v>45616</v>
       </c>
       <c r="C413" s="2">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>5</v>
@@ -6202,10 +6202,10 @@
         <v>1</v>
       </c>
       <c r="B414" s="2">
-        <v>45615</v>
+        <v>45616</v>
       </c>
       <c r="C414" s="2">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>5</v>
@@ -6216,10 +6216,10 @@
         <v>1</v>
       </c>
       <c r="B415" s="2">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="C415" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>5</v>
@@ -6230,13 +6230,13 @@
         <v>1</v>
       </c>
       <c r="B416" s="2">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="C416" s="2">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6247,7 +6247,7 @@
         <v>45618</v>
       </c>
       <c r="C417" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="D417" s="2" t="s">
         <v>5</v>
@@ -6258,10 +6258,10 @@
         <v>1</v>
       </c>
       <c r="B418" s="2">
-        <v>45620</v>
+        <v>45619</v>
       </c>
       <c r="C418" s="2">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="D418" s="2" t="s">
         <v>5</v>
@@ -6275,10 +6275,10 @@
         <v>45620</v>
       </c>
       <c r="C419" s="2">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6289,7 +6289,7 @@
         <v>45620</v>
       </c>
       <c r="C420" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D420" s="2" t="s">
         <v>5</v>
@@ -6303,10 +6303,10 @@
         <v>45621</v>
       </c>
       <c r="C421" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6314,10 +6314,10 @@
         <v>1</v>
       </c>
       <c r="B422" s="2">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C422" s="2">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="D422" s="2" t="s">
         <v>5</v>
@@ -6328,13 +6328,13 @@
         <v>1</v>
       </c>
       <c r="B423" s="2">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="C423" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6345,10 +6345,10 @@
         <v>45624</v>
       </c>
       <c r="C424" s="2">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6356,13 +6356,13 @@
         <v>1</v>
       </c>
       <c r="B425" s="2">
-        <v>45626</v>
+        <v>45624</v>
       </c>
       <c r="C425" s="2">
+        <v>3</v>
+      </c>
+      <c r="D425" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D425" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6370,10 +6370,10 @@
         <v>1</v>
       </c>
       <c r="B426" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C426" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>5</v>
@@ -6384,13 +6384,13 @@
         <v>1</v>
       </c>
       <c r="B427" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C427" s="2">
-        <v>1</v>
+        <v>410</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6401,10 +6401,10 @@
         <v>45627</v>
       </c>
       <c r="C428" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6412,13 +6412,13 @@
         <v>1</v>
       </c>
       <c r="B429" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C429" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6426,13 +6426,13 @@
         <v>1</v>
       </c>
       <c r="B430" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C430" s="2">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6443,10 +6443,10 @@
         <v>45633</v>
       </c>
       <c r="C431" s="2">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6454,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="B432" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C432" s="2">
         <v>2</v>
@@ -6468,13 +6468,13 @@
         <v>1</v>
       </c>
       <c r="B433" s="2">
-        <v>45636</v>
+        <v>45634</v>
       </c>
       <c r="C433" s="2">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6482,10 +6482,10 @@
         <v>1</v>
       </c>
       <c r="B434" s="2">
-        <v>45637</v>
+        <v>45634</v>
       </c>
       <c r="C434" s="2">
-        <v>514</v>
+        <v>1</v>
       </c>
       <c r="D434" s="2" t="s">
         <v>5</v>
@@ -6496,13 +6496,13 @@
         <v>1</v>
       </c>
       <c r="B435" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C435" s="2">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6510,13 +6510,13 @@
         <v>1</v>
       </c>
       <c r="B436" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C436" s="2">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6527,10 +6527,10 @@
         <v>45639</v>
       </c>
       <c r="C437" s="2">
-        <v>265</v>
+        <v>1</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6538,10 +6538,10 @@
         <v>1</v>
       </c>
       <c r="B438" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C438" s="2">
-        <v>1413</v>
+        <v>1</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>5</v>
@@ -6552,10 +6552,10 @@
         <v>1</v>
       </c>
       <c r="B439" s="2">
-        <v>45642</v>
+        <v>45639</v>
       </c>
       <c r="C439" s="2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>5</v>
@@ -6566,10 +6566,10 @@
         <v>1</v>
       </c>
       <c r="B440" s="2">
-        <v>45642</v>
+        <v>45640</v>
       </c>
       <c r="C440" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>5</v>
@@ -6580,10 +6580,10 @@
         <v>1</v>
       </c>
       <c r="B441" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C441" s="2">
-        <v>7</v>
+        <v>1125</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>5</v>
@@ -6594,13 +6594,13 @@
         <v>1</v>
       </c>
       <c r="B442" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C442" s="2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6608,10 +6608,10 @@
         <v>1</v>
       </c>
       <c r="B443" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C443" s="2">
-        <v>468</v>
+        <v>1</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>5</v>
@@ -6622,10 +6622,10 @@
         <v>1</v>
       </c>
       <c r="B444" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C444" s="2">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>5</v>
@@ -6636,10 +6636,10 @@
         <v>1</v>
       </c>
       <c r="B445" s="2">
-        <v>45644</v>
+        <v>45642</v>
       </c>
       <c r="C445" s="2">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>5</v>
@@ -6650,7 +6650,7 @@
         <v>1</v>
       </c>
       <c r="B446" s="2">
-        <v>45645</v>
+        <v>45643</v>
       </c>
       <c r="C446" s="2">
         <v>2</v>
@@ -6664,13 +6664,13 @@
         <v>1</v>
       </c>
       <c r="B447" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C447" s="2">
-        <v>160</v>
+        <v>497</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6678,10 +6678,10 @@
         <v>1</v>
       </c>
       <c r="B448" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C448" s="2">
-        <v>838</v>
+        <v>126</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>5</v>
@@ -6692,13 +6692,13 @@
         <v>1</v>
       </c>
       <c r="B449" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C449" s="2">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6709,7 +6709,7 @@
         <v>45646</v>
       </c>
       <c r="C450" s="2">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="D450" s="2" t="s">
         <v>5</v>
@@ -6723,10 +6723,10 @@
         <v>45647</v>
       </c>
       <c r="C451" s="2">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6734,13 +6734,13 @@
         <v>1</v>
       </c>
       <c r="B452" s="2">
-        <v>45649</v>
+        <v>45647</v>
       </c>
       <c r="C452" s="2">
-        <v>363</v>
+        <v>1269</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6748,10 +6748,10 @@
         <v>1</v>
       </c>
       <c r="B453" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C453" s="2">
-        <v>75</v>
+        <v>139</v>
       </c>
       <c r="D453" s="2" t="s">
         <v>5</v>
@@ -6762,10 +6762,10 @@
         <v>1</v>
       </c>
       <c r="B454" s="2">
-        <v>45650</v>
+        <v>45648</v>
       </c>
       <c r="C454" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D454" s="2" t="s">
         <v>5</v>
@@ -6776,10 +6776,10 @@
         <v>1</v>
       </c>
       <c r="B455" s="2">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="C455" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D455" s="2" t="s">
         <v>5</v>
@@ -6790,13 +6790,13 @@
         <v>1</v>
       </c>
       <c r="B456" s="2">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="C456" s="2">
-        <v>324</v>
+        <v>10</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6804,13 +6804,13 @@
         <v>1</v>
       </c>
       <c r="B457" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C457" s="2">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6818,10 +6818,10 @@
         <v>1</v>
       </c>
       <c r="B458" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C458" s="2">
-        <v>1</v>
+        <v>963</v>
       </c>
       <c r="D458" s="2" t="s">
         <v>5</v>
@@ -6832,13 +6832,13 @@
         <v>1</v>
       </c>
       <c r="B459" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C459" s="2">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6846,10 +6846,10 @@
         <v>1</v>
       </c>
       <c r="B460" s="2">
-        <v>45655</v>
+        <v>45651</v>
       </c>
       <c r="C460" s="2">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="D460" s="2" t="s">
         <v>5</v>
@@ -6860,13 +6860,13 @@
         <v>1</v>
       </c>
       <c r="B461" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C461" s="2">
-        <v>3</v>
+        <v>495</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6874,10 +6874,10 @@
         <v>1</v>
       </c>
       <c r="B462" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C462" s="2">
-        <v>-3</v>
+        <v>29</v>
       </c>
       <c r="D462" s="2" t="s">
         <v>7</v>
@@ -6888,10 +6888,10 @@
         <v>1</v>
       </c>
       <c r="B463" s="2">
-        <v>45658</v>
+        <v>45654</v>
       </c>
       <c r="C463" s="2">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="D463" s="2" t="s">
         <v>5</v>
@@ -6902,13 +6902,13 @@
         <v>1</v>
       </c>
       <c r="B464" s="2">
-        <v>45658</v>
+        <v>45655</v>
       </c>
       <c r="C464" s="2">
-        <v>8</v>
+        <v>2640</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6916,10 +6916,10 @@
         <v>1</v>
       </c>
       <c r="B465" s="2">
-        <v>45659</v>
+        <v>45656</v>
       </c>
       <c r="C465" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D465" s="2" t="s">
         <v>5</v>
@@ -6930,13 +6930,13 @@
         <v>1</v>
       </c>
       <c r="B466" s="2">
-        <v>45659</v>
+        <v>45656</v>
       </c>
       <c r="C466" s="2">
-        <v>311</v>
+        <v>808</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6944,13 +6944,13 @@
         <v>1</v>
       </c>
       <c r="B467" s="2">
-        <v>45659</v>
+        <v>45657</v>
       </c>
       <c r="C467" s="2">
-        <v>2084</v>
+        <v>313</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6958,13 +6958,13 @@
         <v>1</v>
       </c>
       <c r="B468" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C468" s="2">
-        <v>25</v>
+        <v>2335</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6972,10 +6972,10 @@
         <v>1</v>
       </c>
       <c r="B469" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C469" s="2">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>5</v>
@@ -6986,13 +6986,13 @@
         <v>1</v>
       </c>
       <c r="B470" s="2">
-        <v>45602</v>
+        <v>45659</v>
       </c>
       <c r="C470" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -7000,13 +7000,13 @@
         <v>1</v>
       </c>
       <c r="B471" s="2">
-        <v>45605</v>
+        <v>45660</v>
       </c>
       <c r="C471" s="2">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -7014,13 +7014,13 @@
         <v>1</v>
       </c>
       <c r="B472" s="2">
-        <v>45605</v>
+        <v>45660</v>
       </c>
       <c r="C472" s="2">
-        <v>760</v>
+        <v>303</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7028,13 +7028,13 @@
         <v>1</v>
       </c>
       <c r="B473" s="2">
-        <v>45606</v>
+        <v>45661</v>
       </c>
       <c r="C473" s="2">
-        <v>43</v>
+        <v>1656</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7042,13 +7042,13 @@
         <v>1</v>
       </c>
       <c r="B474" s="2">
-        <v>45611</v>
+        <v>45601</v>
       </c>
       <c r="C474" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7056,10 +7056,10 @@
         <v>1</v>
       </c>
       <c r="B475" s="2">
-        <v>45613</v>
+        <v>45604</v>
       </c>
       <c r="C475" s="2">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="D475" s="2" t="s">
         <v>6</v>
@@ -7070,10 +7070,10 @@
         <v>1</v>
       </c>
       <c r="B476" s="2">
-        <v>45614</v>
+        <v>45605</v>
       </c>
       <c r="C476" s="2">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>5</v>
@@ -7084,13 +7084,13 @@
         <v>1</v>
       </c>
       <c r="B477" s="2">
-        <v>45614</v>
+        <v>45607</v>
       </c>
       <c r="C477" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7098,13 +7098,13 @@
         <v>1</v>
       </c>
       <c r="B478" s="2">
-        <v>45616</v>
+        <v>45613</v>
       </c>
       <c r="C478" s="2">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7112,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="B479" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C479" s="2">
         <v>4</v>
@@ -7126,13 +7126,13 @@
         <v>1</v>
       </c>
       <c r="B480" s="2">
-        <v>45619</v>
+        <v>45614</v>
       </c>
       <c r="C480" s="2">
-        <v>224</v>
+        <v>60</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7140,10 +7140,10 @@
         <v>1</v>
       </c>
       <c r="B481" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C481" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D481" s="2" t="s">
         <v>5</v>
@@ -7154,13 +7154,13 @@
         <v>1</v>
       </c>
       <c r="B482" s="2">
-        <v>45621</v>
+        <v>45617</v>
       </c>
       <c r="C482" s="2">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7168,10 +7168,10 @@
         <v>1</v>
       </c>
       <c r="B483" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C483" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D483" s="2" t="s">
         <v>5</v>
@@ -7182,13 +7182,13 @@
         <v>1</v>
       </c>
       <c r="B484" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C484" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7196,10 +7196,10 @@
         <v>1</v>
       </c>
       <c r="B485" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C485" s="2">
-        <v>707</v>
+        <v>412</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>5</v>
@@ -7210,10 +7210,10 @@
         <v>1</v>
       </c>
       <c r="B486" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C486" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D486" s="2" t="s">
         <v>5</v>
@@ -7224,13 +7224,13 @@
         <v>1</v>
       </c>
       <c r="B487" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C487" s="2">
+        <v>349</v>
+      </c>
+      <c r="D487" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D487" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7238,10 +7238,10 @@
         <v>1</v>
       </c>
       <c r="B488" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C488" s="2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>5</v>
@@ -7252,10 +7252,10 @@
         <v>1</v>
       </c>
       <c r="B489" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C489" s="2">
-        <v>1</v>
+        <v>957</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>5</v>
@@ -7266,10 +7266,10 @@
         <v>1</v>
       </c>
       <c r="B490" s="2">
-        <v>45627</v>
+        <v>45625</v>
       </c>
       <c r="C490" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D490" s="2" t="s">
         <v>5</v>
@@ -7280,10 +7280,10 @@
         <v>1</v>
       </c>
       <c r="B491" s="2">
-        <v>45628</v>
+        <v>45626</v>
       </c>
       <c r="C491" s="2">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>5</v>
@@ -7294,13 +7294,13 @@
         <v>1</v>
       </c>
       <c r="B492" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C492" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7308,10 +7308,10 @@
         <v>1</v>
       </c>
       <c r="B493" s="2">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C493" s="2">
-        <v>3</v>
+        <v>1018</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>5</v>
@@ -7322,13 +7322,13 @@
         <v>1</v>
       </c>
       <c r="B494" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C494" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7336,10 +7336,10 @@
         <v>1</v>
       </c>
       <c r="B495" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C495" s="2">
-        <v>417</v>
+        <v>88</v>
       </c>
       <c r="D495" s="2" t="s">
         <v>5</v>
@@ -7350,10 +7350,10 @@
         <v>1</v>
       </c>
       <c r="B496" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C496" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D496" s="2" t="s">
         <v>5</v>
@@ -7364,13 +7364,13 @@
         <v>1</v>
       </c>
       <c r="B497" s="2">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C497" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7378,10 +7378,10 @@
         <v>1</v>
       </c>
       <c r="B498" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C498" s="2">
-        <v>2</v>
+        <v>392</v>
       </c>
       <c r="D498" s="2" t="s">
         <v>5</v>
@@ -7392,13 +7392,13 @@
         <v>1</v>
       </c>
       <c r="B499" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C499" s="2">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7406,10 +7406,10 @@
         <v>1</v>
       </c>
       <c r="B500" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C500" s="2">
-        <v>1260</v>
+        <v>2</v>
       </c>
       <c r="D500" s="2" t="s">
         <v>5</v>
@@ -7420,10 +7420,10 @@
         <v>1</v>
       </c>
       <c r="B501" s="2">
-        <v>45635</v>
+        <v>45631</v>
       </c>
       <c r="C501" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>5</v>
@@ -7434,10 +7434,10 @@
         <v>1</v>
       </c>
       <c r="B502" s="2">
-        <v>45635</v>
+        <v>45632</v>
       </c>
       <c r="C502" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D502" s="2" t="s">
         <v>5</v>
@@ -7448,13 +7448,13 @@
         <v>1</v>
       </c>
       <c r="B503" s="2">
-        <v>45636</v>
+        <v>45633</v>
       </c>
       <c r="C503" s="2">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7462,13 +7462,13 @@
         <v>1</v>
       </c>
       <c r="B504" s="2">
-        <v>45637</v>
+        <v>45633</v>
       </c>
       <c r="C504" s="2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7476,10 +7476,10 @@
         <v>1</v>
       </c>
       <c r="B505" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C505" s="2">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="D505" s="2" t="s">
         <v>5</v>
@@ -7490,13 +7490,13 @@
         <v>1</v>
       </c>
       <c r="B506" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C506" s="2">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7504,13 +7504,13 @@
         <v>1</v>
       </c>
       <c r="B507" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C507" s="2">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7518,10 +7518,10 @@
         <v>1</v>
       </c>
       <c r="B508" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C508" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D508" s="2" t="s">
         <v>5</v>
@@ -7532,13 +7532,13 @@
         <v>1</v>
       </c>
       <c r="B509" s="2">
-        <v>45642</v>
+        <v>45639</v>
       </c>
       <c r="C509" s="2">
-        <v>384</v>
+        <v>2</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7546,10 +7546,10 @@
         <v>1</v>
       </c>
       <c r="B510" s="2">
-        <v>45643</v>
+        <v>45640</v>
       </c>
       <c r="C510" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D510" s="2" t="s">
         <v>5</v>
@@ -7560,13 +7560,13 @@
         <v>1</v>
       </c>
       <c r="B511" s="2">
-        <v>45644</v>
+        <v>45640</v>
       </c>
       <c r="C511" s="2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7574,13 +7574,13 @@
         <v>1</v>
       </c>
       <c r="B512" s="2">
-        <v>45645</v>
+        <v>45642</v>
       </c>
       <c r="C512" s="2">
-        <v>555</v>
+        <v>1</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7588,10 +7588,10 @@
         <v>1</v>
       </c>
       <c r="B513" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C513" s="2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D513" s="2" t="s">
         <v>5</v>
@@ -7602,10 +7602,10 @@
         <v>1</v>
       </c>
       <c r="B514" s="2">
-        <v>45647</v>
+        <v>45645</v>
       </c>
       <c r="C514" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D514" s="2" t="s">
         <v>5</v>
@@ -7616,13 +7616,13 @@
         <v>1</v>
       </c>
       <c r="B515" s="2">
-        <v>45647</v>
+        <v>45645</v>
       </c>
       <c r="C515" s="2">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7630,13 +7630,13 @@
         <v>1</v>
       </c>
       <c r="B516" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C516" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7644,13 +7644,13 @@
         <v>1</v>
       </c>
       <c r="B517" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C517" s="2">
-        <v>935</v>
+        <v>571</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7658,10 +7658,10 @@
         <v>1</v>
       </c>
       <c r="B518" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C518" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>5</v>
@@ -7686,13 +7686,13 @@
         <v>1</v>
       </c>
       <c r="B520" s="2">
-        <v>45650</v>
+        <v>45649</v>
       </c>
       <c r="C520" s="2">
-        <v>5</v>
+        <v>216</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7700,13 +7700,13 @@
         <v>1</v>
       </c>
       <c r="B521" s="2">
-        <v>45650</v>
+        <v>45649</v>
       </c>
       <c r="C521" s="2">
-        <v>304</v>
+        <v>1208</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7714,10 +7714,10 @@
         <v>1</v>
       </c>
       <c r="B522" s="2">
-        <v>45652</v>
+        <v>45651</v>
       </c>
       <c r="C522" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D522" s="2" t="s">
         <v>5</v>
@@ -7731,7 +7731,7 @@
         <v>45652</v>
       </c>
       <c r="C523" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D523" s="2" t="s">
         <v>5</v>
@@ -7742,13 +7742,13 @@
         <v>1</v>
       </c>
       <c r="B524" s="2">
-        <v>45655</v>
+        <v>45652</v>
       </c>
       <c r="C524" s="2">
-        <v>1</v>
+        <v>1348</v>
       </c>
       <c r="D524" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7756,10 +7756,10 @@
         <v>1</v>
       </c>
       <c r="B525" s="2">
-        <v>45655</v>
+        <v>45652</v>
       </c>
       <c r="C525" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D525" s="2" t="s">
         <v>5</v>
@@ -7770,10 +7770,10 @@
         <v>1</v>
       </c>
       <c r="B526" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C526" s="2">
-        <v>2</v>
+        <v>1317</v>
       </c>
       <c r="D526" s="2" t="s">
         <v>5</v>
@@ -7784,10 +7784,10 @@
         <v>1</v>
       </c>
       <c r="B527" s="2">
-        <v>45655</v>
+        <v>45654</v>
       </c>
       <c r="C527" s="2">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D527" s="2" t="s">
         <v>5</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="B528" s="2">
-        <v>45656</v>
+        <v>45655</v>
       </c>
       <c r="C528" s="2">
         <v>2</v>
@@ -7815,7 +7815,7 @@
         <v>45656</v>
       </c>
       <c r="C529" s="2">
-        <v>4</v>
+        <v>1215</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>5</v>
@@ -7829,7 +7829,7 @@
         <v>45657</v>
       </c>
       <c r="C530" s="2">
-        <v>1383</v>
+        <v>95</v>
       </c>
       <c r="D530" s="2" t="s">
         <v>5</v>
@@ -7843,7 +7843,7 @@
         <v>45658</v>
       </c>
       <c r="C531" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D531" s="2" t="s">
         <v>5</v>
@@ -7854,13 +7854,13 @@
         <v>1</v>
       </c>
       <c r="B532" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C532" s="2">
-        <v>2</v>
+        <v>712</v>
       </c>
       <c r="D532" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7868,10 +7868,10 @@
         <v>1</v>
       </c>
       <c r="B533" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C533" s="2">
-        <v>147</v>
+        <v>1567</v>
       </c>
       <c r="D533" s="2" t="s">
         <v>5</v>
@@ -7885,7 +7885,7 @@
         <v>45659</v>
       </c>
       <c r="C534" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D534" s="2" t="s">
         <v>5</v>
@@ -7896,10 +7896,10 @@
         <v>1</v>
       </c>
       <c r="B535" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C535" s="2">
-        <v>1733</v>
+        <v>175</v>
       </c>
       <c r="D535" s="2" t="s">
         <v>5</v>
@@ -7910,10 +7910,10 @@
         <v>1</v>
       </c>
       <c r="B536" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C536" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D536" s="2" t="s">
         <v>5</v>
@@ -7941,7 +7941,7 @@
         <v>45661</v>
       </c>
       <c r="C538" s="2">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>5</v>
